--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5184BA3-A582-4120-8A27-B1992B5D0386}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{066B19A1-24D6-465B-ABC8-922C1E1DF0AF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="12" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,13 @@
     <sheet name="MountainWest" sheetId="9" r:id="rId9"/>
     <sheet name="SEC" sheetId="10" r:id="rId10"/>
     <sheet name="WCC" sheetId="11" r:id="rId11"/>
+    <sheet name="American" sheetId="12" r:id="rId12"/>
+    <sheet name="BigSouth" sheetId="13" r:id="rId13"/>
+    <sheet name="CAA" sheetId="14" r:id="rId14"/>
+    <sheet name="CUSA" sheetId="15" r:id="rId15"/>
+    <sheet name="Patriot" sheetId="16" r:id="rId16"/>
+    <sheet name="Southern" sheetId="17" r:id="rId17"/>
+    <sheet name="Southland" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="241">
   <si>
     <t>Team</t>
   </si>
@@ -598,6 +605,177 @@
   </si>
   <si>
     <t>Cal Baptist</t>
+  </si>
+  <si>
+    <t>Tulsa</t>
+  </si>
+  <si>
+    <t>Wichita St</t>
+  </si>
+  <si>
+    <t>UAB</t>
+  </si>
+  <si>
+    <t>FL Atlantic</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Tulane</t>
+  </si>
+  <si>
+    <t>Temple</t>
+  </si>
+  <si>
+    <t>Memphis</t>
+  </si>
+  <si>
+    <t>Winthrop</t>
+  </si>
+  <si>
+    <t>Radford</t>
+  </si>
+  <si>
+    <t>UNC Asheville</t>
+  </si>
+  <si>
+    <t>Longwood</t>
+  </si>
+  <si>
+    <t>Charleston So</t>
+  </si>
+  <si>
+    <t>SC Upstate</t>
+  </si>
+  <si>
+    <t>Gardner Webb</t>
+  </si>
+  <si>
+    <t>Col Charleston</t>
+  </si>
+  <si>
+    <t>Hofstra</t>
+  </si>
+  <si>
+    <t>Monmouth</t>
+  </si>
+  <si>
+    <t>Drexel</t>
+  </si>
+  <si>
+    <t>William &amp; Mary</t>
+  </si>
+  <si>
+    <t>Towson</t>
+  </si>
+  <si>
+    <t>Stony Brook</t>
+  </si>
+  <si>
+    <t>Campbell</t>
+  </si>
+  <si>
+    <t>Hampton</t>
+  </si>
+  <si>
+    <t>Elon</t>
+  </si>
+  <si>
+    <t>NC A&amp;T</t>
+  </si>
+  <si>
+    <t>Northeastern</t>
+  </si>
+  <si>
+    <t>Sam Houston St</t>
+  </si>
+  <si>
+    <t>WKU</t>
+  </si>
+  <si>
+    <t>MTSU</t>
+  </si>
+  <si>
+    <t>Kennesaw</t>
+  </si>
+  <si>
+    <t>Louisiana Tech</t>
+  </si>
+  <si>
+    <t>Jacksonville St</t>
+  </si>
+  <si>
+    <t>Missouri St</t>
+  </si>
+  <si>
+    <t>Florida Intl</t>
+  </si>
+  <si>
+    <t>New Mexico St</t>
+  </si>
+  <si>
+    <t>Lehigh</t>
+  </si>
+  <si>
+    <t>Colgate</t>
+  </si>
+  <si>
+    <t>Boston Univ</t>
+  </si>
+  <si>
+    <t>Mercer</t>
+  </si>
+  <si>
+    <t>Wofford</t>
+  </si>
+  <si>
+    <t>Samford</t>
+  </si>
+  <si>
+    <t>W Carolina</t>
+  </si>
+  <si>
+    <t>Furman</t>
+  </si>
+  <si>
+    <t>UNC Greensboro</t>
+  </si>
+  <si>
+    <t>Chattanooga</t>
+  </si>
+  <si>
+    <t>Citadel</t>
+  </si>
+  <si>
+    <t>VMI</t>
+  </si>
+  <si>
+    <t>McNeese St</t>
+  </si>
+  <si>
+    <t>UTRGV</t>
+  </si>
+  <si>
+    <t>TAM C. Christi</t>
+  </si>
+  <si>
+    <t>New Orleans</t>
+  </si>
+  <si>
+    <t>Nicholls St</t>
+  </si>
+  <si>
+    <t>Houston Chr</t>
+  </si>
+  <si>
+    <t>Northwestern LA</t>
+  </si>
+  <si>
+    <t>Presbyterian</t>
   </si>
 </sst>
 </file>
@@ -2037,6 +2215,681 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80ECFDF5-28A3-4A49-93EF-E1982AF1B4A9}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BF231B-6A21-4AE7-AB70-19352D564142}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E5C766-0E1F-4378-9006-A2820FD9340E}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FA2769-8E6F-4BC5-8787-2A317AF7B89B}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01990E71-BED3-4F35-A78E-5A1E245FBFC1}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D5E716-31D5-49B6-B0B8-0130AB45E7C8}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBA5F6B-8732-486F-BD4B-28C914059894}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1E2147-A618-41F0-9220-B1F032539E0E}">
   <dimension ref="A1:B18"/>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{066B19A1-24D6-465B-ABC8-922C1E1DF0AF}"/>
+  <xr:revisionPtr revIDLastSave="260" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5463424-5DB8-40AA-8FB8-33587EA271BF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="12" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="260" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5463424-5DB8-40AA-8FB8-33587EA271BF}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF59166-924F-46DC-80D5-AB780EF9B925}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>183</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
         <v>58</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="B65" t="s">
         <v>76</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="B66" t="s">
         <v>76</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF59166-924F-46DC-80D5-AB780EF9B925}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42634184-C253-4CB8-AECC-3EB6F1F6BEF5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="10" activeTab="17" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -3256,7 +3256,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3669,7 +3669,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3852,7 +3852,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3868,7 +3868,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3884,7 +3884,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42634184-C253-4CB8-AECC-3EB6F1F6BEF5}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F2EA9D6-60F6-48E7-A9C3-E28896F18ED3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="10" activeTab="17" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="8" activeTab="9" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -1320,7 +1320,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
@@ -1386,7 +1386,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -1441,7 +1441,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1474,216 +1474,216 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
         <v>58</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
         <v>58</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
         <v>58</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
         <v>58</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
         <v>58</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
         <v>58</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
         <v>58</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B48" t="s">
         <v>58</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="B49" t="s">
         <v>58</v>
@@ -1716,7 +1716,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="B51" t="s">
         <v>58</v>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B53" t="s">
         <v>58</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
         <v>76</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
         <v>76</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="B61" t="s">
         <v>76</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B62" t="s">
         <v>76</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B63" t="s">
         <v>76</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
         <v>76</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
         <v>76</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B69" t="s">
         <v>76</v>
@@ -1989,7 +1989,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2972,7 +2972,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3224,7 +3224,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3240,7 +3240,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3256,7 +3256,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3433,7 +3433,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3511,7 +3511,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -3567,7 +3567,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F2EA9D6-60F6-48E7-A9C3-E28896F18ED3}"/>
+  <xr:revisionPtr revIDLastSave="686" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2841127-17FE-4447-9389-A2AFC8DC1E69}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="8" activeTab="9" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="31" activeTab="31" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,20 @@
     <sheet name="Patriot" sheetId="16" r:id="rId16"/>
     <sheet name="Southern" sheetId="17" r:id="rId17"/>
     <sheet name="Southland" sheetId="18" r:id="rId18"/>
+    <sheet name="AmericaEast" sheetId="19" r:id="rId19"/>
+    <sheet name="AtlanticSun" sheetId="20" r:id="rId20"/>
+    <sheet name="BigSky" sheetId="21" r:id="rId21"/>
+    <sheet name="BigWest" sheetId="22" r:id="rId22"/>
+    <sheet name="Horizon" sheetId="23" r:id="rId23"/>
+    <sheet name="Ivy" sheetId="24" r:id="rId24"/>
+    <sheet name="MAAC" sheetId="25" r:id="rId25"/>
+    <sheet name="MEAC" sheetId="26" r:id="rId26"/>
+    <sheet name="Northeast" sheetId="27" r:id="rId27"/>
+    <sheet name="OhioValley" sheetId="28" r:id="rId28"/>
+    <sheet name="SWAC" sheetId="29" r:id="rId29"/>
+    <sheet name="Summit" sheetId="30" r:id="rId30"/>
+    <sheet name="SunBelt" sheetId="31" r:id="rId31"/>
+    <sheet name="WAC" sheetId="32" r:id="rId32"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="363">
   <si>
     <t>Team</t>
   </si>
@@ -776,6 +790,372 @@
   </si>
   <si>
     <t>Presbyterian</t>
+  </si>
+  <si>
+    <t>NJIT</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>MA Lowell</t>
+  </si>
+  <si>
+    <t>Albany</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Bryant</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>Austin Peay</t>
+  </si>
+  <si>
+    <t>Queens NC</t>
+  </si>
+  <si>
+    <t>Lipscomb</t>
+  </si>
+  <si>
+    <t>FGCU</t>
+  </si>
+  <si>
+    <t>West Georgia</t>
+  </si>
+  <si>
+    <t>E Kentucky</t>
+  </si>
+  <si>
+    <t>Bellarmine</t>
+  </si>
+  <si>
+    <t>Jacksonville</t>
+  </si>
+  <si>
+    <t>Stetson</t>
+  </si>
+  <si>
+    <t>North Florida</t>
+  </si>
+  <si>
+    <t>North Alabama</t>
+  </si>
+  <si>
+    <t>Montana St</t>
+  </si>
+  <si>
+    <t>E Washington</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Weber St</t>
+  </si>
+  <si>
+    <t>N Colorado</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>Idaho St</t>
+  </si>
+  <si>
+    <t>Northern Arizona</t>
+  </si>
+  <si>
+    <t>CS Sacramento</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>CS Fullerton</t>
+  </si>
+  <si>
+    <t>CS Northridge</t>
+  </si>
+  <si>
+    <t>UC San Diego</t>
+  </si>
+  <si>
+    <t>UC Davis</t>
+  </si>
+  <si>
+    <t>UC Santa Barbara</t>
+  </si>
+  <si>
+    <t>Cal Poly</t>
+  </si>
+  <si>
+    <t>American Univ</t>
+  </si>
+  <si>
+    <t>Loyola MD</t>
+  </si>
+  <si>
+    <t>Lafayette</t>
+  </si>
+  <si>
+    <t>Bucknell</t>
+  </si>
+  <si>
+    <t>Army</t>
+  </si>
+  <si>
+    <t>Holy Cross</t>
+  </si>
+  <si>
+    <t>Robert Morris</t>
+  </si>
+  <si>
+    <t>Detroit</t>
+  </si>
+  <si>
+    <t>Oakland</t>
+  </si>
+  <si>
+    <t>WI Green Bay</t>
+  </si>
+  <si>
+    <t>PFW</t>
+  </si>
+  <si>
+    <t>N Kentucky</t>
+  </si>
+  <si>
+    <t>WI Milwaukee</t>
+  </si>
+  <si>
+    <t>Youngstown St</t>
+  </si>
+  <si>
+    <t>Cleveland St</t>
+  </si>
+  <si>
+    <t>IUPUI</t>
+  </si>
+  <si>
+    <t>Harvard</t>
+  </si>
+  <si>
+    <t>Penn</t>
+  </si>
+  <si>
+    <t>Cornell</t>
+  </si>
+  <si>
+    <t>St Peter's</t>
+  </si>
+  <si>
+    <t>Siena</t>
+  </si>
+  <si>
+    <t>Quinnipiac</t>
+  </si>
+  <si>
+    <t>Marist</t>
+  </si>
+  <si>
+    <t>Mt St Mary's</t>
+  </si>
+  <si>
+    <t>Fairfield</t>
+  </si>
+  <si>
+    <t>Iona</t>
+  </si>
+  <si>
+    <t>Sacred Heart</t>
+  </si>
+  <si>
+    <t>Manhattan</t>
+  </si>
+  <si>
+    <t>Morgan St</t>
+  </si>
+  <si>
+    <t>NC Central</t>
+  </si>
+  <si>
+    <t>Norfolk St</t>
+  </si>
+  <si>
+    <t>S Carolina St</t>
+  </si>
+  <si>
+    <t>MD E Shore</t>
+  </si>
+  <si>
+    <t>Delaware St</t>
+  </si>
+  <si>
+    <t>LIU Brooklyn</t>
+  </si>
+  <si>
+    <t>Central Conn</t>
+  </si>
+  <si>
+    <t>Mercyhurst</t>
+  </si>
+  <si>
+    <t>Le Moyne</t>
+  </si>
+  <si>
+    <t>Stonehill</t>
+  </si>
+  <si>
+    <t>F Dickinson</t>
+  </si>
+  <si>
+    <t>Wagner</t>
+  </si>
+  <si>
+    <t>Chicago St</t>
+  </si>
+  <si>
+    <t>Morehead St</t>
+  </si>
+  <si>
+    <t>SE Missouri St</t>
+  </si>
+  <si>
+    <t>TN Martin</t>
+  </si>
+  <si>
+    <t>SIUE</t>
+  </si>
+  <si>
+    <t>Lindenwood</t>
+  </si>
+  <si>
+    <t>Ark Little Rock</t>
+  </si>
+  <si>
+    <t>E Illinois</t>
+  </si>
+  <si>
+    <t>Bethune-Cookman</t>
+  </si>
+  <si>
+    <t>Florida A&amp;M</t>
+  </si>
+  <si>
+    <t>Southern Univ</t>
+  </si>
+  <si>
+    <t>TX Southern</t>
+  </si>
+  <si>
+    <t>Alabama A&amp;M</t>
+  </si>
+  <si>
+    <t>Ark Pine Bluff</t>
+  </si>
+  <si>
+    <t>Jackson St</t>
+  </si>
+  <si>
+    <t>Prairie View</t>
+  </si>
+  <si>
+    <t>Grambling</t>
+  </si>
+  <si>
+    <t>Alabama St</t>
+  </si>
+  <si>
+    <t>Alcorn St</t>
+  </si>
+  <si>
+    <t>MS Valley St</t>
+  </si>
+  <si>
+    <t>St Thomas MN</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>NE Omaha</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>S Dakota St</t>
+  </si>
+  <si>
+    <t>Oral Roberts</t>
+  </si>
+  <si>
+    <t>Missouri KC</t>
+  </si>
+  <si>
+    <t>Marshall</t>
+  </si>
+  <si>
+    <t>Coastal Car</t>
+  </si>
+  <si>
+    <t>Appalachian St</t>
+  </si>
+  <si>
+    <t>Texas St</t>
+  </si>
+  <si>
+    <t>South Alabama</t>
+  </si>
+  <si>
+    <t>Arkansas St</t>
+  </si>
+  <si>
+    <t>Southern Miss</t>
+  </si>
+  <si>
+    <t>James Madison</t>
+  </si>
+  <si>
+    <t>Ga Southern</t>
+  </si>
+  <si>
+    <t>Old Dominion</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Georgia St</t>
+  </si>
+  <si>
+    <t>ULM</t>
+  </si>
+  <si>
+    <t>Utah Valley</t>
+  </si>
+  <si>
+    <t>Utah Tech</t>
+  </si>
+  <si>
+    <t>UT Arlington</t>
+  </si>
+  <si>
+    <t>Southern Utah</t>
+  </si>
+  <si>
+    <t>Abilene Chr</t>
+  </si>
+  <si>
+    <t>Tarleton St</t>
   </si>
 </sst>
 </file>
@@ -2241,7 +2621,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2249,7 +2629,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2265,7 +2645,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2273,7 +2653,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2281,7 +2661,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2289,7 +2669,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2297,7 +2677,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2305,7 +2685,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -2641,10 +3021,10 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01990E71-BED3-4F35-A78E-5A1E245FBFC1}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2685,6 +3065,54 @@
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2890,6 +3318,92 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2DBD036-7C25-42A5-9B30-91FF51FF1B7B}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1E2147-A618-41F0-9220-B1F032539E0E}">
   <dimension ref="A1:B18"/>
@@ -3026,6 +3540,959 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5499F9DC-0B88-45C1-96EC-CC04062C1903}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A11CB0E-89E8-49C4-9DF3-1CBF8C343024}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8690B1F7-53FB-446A-8BB6-4017A2A782BF}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38548A91-8485-412C-8463-0D08E7612168}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>289</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F981494-DD68-4A65-A86E-D9D7F697523C}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3489DA-1F0B-43AB-82E1-B94ECF0E407A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>302</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{653EB0C1-E2ED-4445-AF40-949CF2B23D13}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F53E3AE0-DBC7-4EC2-9681-F16A9E98F4E6}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>316</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{311418C4-89A1-4B02-AABB-26769E2310DE}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B37E31-487D-4996-841F-18B70BA33D5D}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>333</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>335</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3190,6 +4657,315 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D9F80B-9BBC-41A5-9AD1-65CDED2CF755}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>343</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADF0F74-AD91-487E-ABF7-F83E18AD6E21}">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>349</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>350</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>352</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>354</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>355</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B16" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463ED8E5-0EDD-4E7A-80E5-2613552CE37A}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F1CD20-BC26-4116-8E9A-A07B1F392CD7}">
   <dimension ref="A1:B18"/>
@@ -3479,7 +5255,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3487,7 +5263,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="686" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2841127-17FE-4447-9389-A2AFC8DC1E69}"/>
+  <xr:revisionPtr revIDLastSave="741" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EEE0B10-FFD2-4D88-BE65-83F0E3C7DA14}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="31" activeTab="31" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -1601,7 +1601,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -1733,7 +1733,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
@@ -1777,7 +1777,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -1821,7 +1821,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1854,216 +1854,216 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>221</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
         <v>58</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
         <v>58</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
         <v>58</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
         <v>58</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>182</v>
       </c>
       <c r="B45" t="s">
         <v>58</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
         <v>58</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="B47" t="s">
         <v>58</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
         <v>58</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>89</v>
+        <v>201</v>
       </c>
       <c r="B50" t="s">
         <v>58</v>
@@ -2107,7 +2107,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="B56" t="s">
         <v>76</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
         <v>76</v>
@@ -2173,7 +2173,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="B58" t="s">
         <v>76</v>
@@ -2184,7 +2184,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
         <v>76</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B60" t="s">
         <v>76</v>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="B61" t="s">
         <v>76</v>
@@ -2217,7 +2217,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B62" t="s">
         <v>76</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
         <v>76</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B64" t="s">
         <v>76</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="B65" t="s">
         <v>76</v>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>183</v>
+        <v>357</v>
       </c>
       <c r="B66" t="s">
         <v>76</v>
@@ -2272,7 +2272,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B67" t="s">
         <v>76</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
         <v>76</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>249</v>
       </c>
       <c r="B69" t="s">
         <v>76</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="741" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EEE0B10-FFD2-4D88-BE65-83F0E3C7DA14}"/>
+  <xr:revisionPtr revIDLastSave="745" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{201AC2DB-6C9B-4E5A-BFA1-7747CDF87280}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="10" activeTab="17" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="745" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{201AC2DB-6C9B-4E5A-BFA1-7747CDF87280}"/>
+  <xr:revisionPtr revIDLastSave="748" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{315D8FDC-F067-4A57-AF31-9C94F2BA1C73}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="10" activeTab="17" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="8" activeTab="8" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="748" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{315D8FDC-F067-4A57-AF31-9C94F2BA1C73}"/>
+  <xr:revisionPtr revIDLastSave="757" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9178A515-E8F8-48FE-9AB8-0FA71E2BFE36}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="8" activeTab="8" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="11" activeTab="11" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2661,7 +2661,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="757" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9178A515-E8F8-48FE-9AB8-0FA71E2BFE36}"/>
+  <xr:revisionPtr revIDLastSave="768" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08D1D3E8-90D5-4EF3-9680-6B62786B6050}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="11" activeTab="11" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="14" activeTab="14" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2975,7 +2975,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="768" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08D1D3E8-90D5-4EF3-9680-6B62786B6050}"/>
+  <xr:revisionPtr revIDLastSave="777" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60A07118-26AE-424F-94B9-87B92881907B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="14" activeTab="14" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
   <sheets>
     <sheet name="NCAA" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="362">
   <si>
     <t>Team</t>
   </si>
@@ -292,9 +292,6 @@
   </si>
   <si>
     <t>Howard</t>
-  </si>
-  <si>
-    <t>Bethune Cookman</t>
   </si>
   <si>
     <t>West</t>
@@ -1645,7 +1642,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -1678,7 +1675,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -1711,7 +1708,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -1722,7 +1719,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>248</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -1788,7 +1785,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -1810,7 +1807,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -1821,7 +1818,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -1843,7 +1840,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1854,7 +1851,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -1865,7 +1862,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
@@ -1920,7 +1917,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
@@ -1931,7 +1928,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
@@ -1975,7 +1972,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
@@ -2008,7 +2005,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
@@ -2019,7 +2016,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
@@ -2030,7 +2027,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B45" t="s">
         <v>58</v>
@@ -2052,7 +2049,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B47" t="s">
         <v>58</v>
@@ -2063,7 +2060,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
         <v>58</v>
@@ -2085,7 +2082,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B50" t="s">
         <v>58</v>
@@ -2107,7 +2104,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>220</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
@@ -2118,7 +2115,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>323</v>
       </c>
       <c r="B53" t="s">
         <v>58</v>
@@ -2129,10 +2126,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>5</v>
@@ -2140,10 +2137,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>6</v>
@@ -2151,10 +2148,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>7</v>
@@ -2165,7 +2162,7 @@
         <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>8</v>
@@ -2176,7 +2173,7 @@
         <v>23</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>9</v>
@@ -2187,7 +2184,7 @@
         <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>10</v>
@@ -2198,7 +2195,7 @@
         <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>11</v>
@@ -2209,7 +2206,7 @@
         <v>50</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>12</v>
@@ -2220,7 +2217,7 @@
         <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>13</v>
@@ -2231,7 +2228,7 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>14</v>
@@ -2242,7 +2239,7 @@
         <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>15</v>
@@ -2250,10 +2247,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>16</v>
@@ -2261,10 +2258,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>17</v>
@@ -2275,7 +2272,7 @@
         <v>54</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>18</v>
@@ -2283,10 +2280,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>19</v>
@@ -2294,10 +2291,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>249</v>
+        <v>56</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>20</v>
@@ -2353,7 +2350,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2401,7 +2398,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2409,7 +2406,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2425,7 +2422,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -2433,7 +2430,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -2441,7 +2438,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -2449,7 +2446,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -2457,7 +2454,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -2465,7 +2462,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -2503,7 +2500,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2519,7 +2516,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2527,7 +2524,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2535,7 +2532,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2543,7 +2540,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2551,7 +2548,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2559,7 +2556,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2567,7 +2564,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -2575,7 +2572,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -2583,7 +2580,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -2621,7 +2618,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2629,7 +2626,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2637,7 +2634,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2645,7 +2642,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2653,7 +2650,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2661,7 +2658,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2669,7 +2666,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2677,7 +2674,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2685,7 +2682,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -2715,7 +2712,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -2723,7 +2720,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2731,7 +2728,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2739,7 +2736,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2747,7 +2744,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2755,7 +2752,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2763,7 +2760,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2771,7 +2768,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2779,7 +2776,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2817,7 +2814,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2825,7 +2822,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2833,7 +2830,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2841,7 +2838,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2849,7 +2846,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2857,7 +2854,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2865,7 +2862,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2873,7 +2870,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2881,7 +2878,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -2889,7 +2886,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -2897,7 +2894,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -2905,7 +2902,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -2943,7 +2940,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2951,7 +2948,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2959,7 +2956,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2967,7 +2964,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2975,7 +2972,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2983,7 +2980,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2991,7 +2988,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2999,7 +2996,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3007,7 +3004,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3037,7 +3034,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3045,7 +3042,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3053,7 +3050,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3061,7 +3058,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3069,7 +3066,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3077,7 +3074,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3085,7 +3082,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3093,7 +3090,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3101,7 +3098,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3109,7 +3106,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3139,7 +3136,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3147,7 +3144,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3155,7 +3152,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3163,7 +3160,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3171,7 +3168,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3179,7 +3176,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3187,7 +3184,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3195,7 +3192,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3203,7 +3200,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3211,7 +3208,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3249,7 +3246,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3257,7 +3254,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3265,7 +3262,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3273,7 +3270,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3281,7 +3278,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3289,7 +3286,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3297,7 +3294,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3344,7 +3341,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3352,7 +3349,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3360,7 +3357,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3368,7 +3365,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3376,7 +3373,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3384,7 +3381,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3392,7 +3389,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3430,7 +3427,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3438,7 +3435,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3446,7 +3443,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3454,7 +3451,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3462,7 +3459,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3470,7 +3467,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3478,7 +3475,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3486,7 +3483,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3494,7 +3491,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3502,7 +3499,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -3510,7 +3507,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -3518,7 +3515,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -3526,7 +3523,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -3565,7 +3562,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3573,7 +3570,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3581,7 +3578,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3589,7 +3586,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3597,7 +3594,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3605,7 +3602,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3613,7 +3610,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3621,7 +3618,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3629,7 +3626,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3637,7 +3634,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3645,7 +3642,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -3653,7 +3650,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -3691,7 +3688,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3699,7 +3696,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3707,7 +3704,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3715,7 +3712,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3723,7 +3720,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3731,7 +3728,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3739,7 +3736,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3747,7 +3744,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3755,7 +3752,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3802,7 +3799,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3810,7 +3807,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3818,7 +3815,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3826,7 +3823,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3834,7 +3831,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3842,7 +3839,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3850,7 +3847,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3888,7 +3885,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3896,7 +3893,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3904,7 +3901,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3912,7 +3909,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3920,7 +3917,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3928,7 +3925,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3936,7 +3933,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3944,7 +3941,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3952,7 +3949,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3960,7 +3957,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -3995,7 +3992,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4003,7 +4000,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4011,7 +4008,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4049,7 +4046,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4057,7 +4054,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4065,7 +4062,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4073,7 +4070,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4081,7 +4078,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4089,7 +4086,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4097,7 +4094,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4105,7 +4102,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4113,7 +4110,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -4152,7 +4149,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4160,7 +4157,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4168,7 +4165,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4176,7 +4173,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4184,7 +4181,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4192,7 +4189,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4222,7 +4219,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4230,7 +4227,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4238,7 +4235,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4246,7 +4243,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4254,7 +4251,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4262,7 +4259,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4270,7 +4267,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4278,7 +4275,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4308,7 +4305,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4316,7 +4313,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4324,7 +4321,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4332,7 +4329,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4340,7 +4337,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4348,7 +4345,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4356,7 +4353,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4364,7 +4361,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4400,7 +4397,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4408,7 +4405,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4416,7 +4413,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4424,7 +4421,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4432,7 +4429,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4440,7 +4437,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4448,7 +4445,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4456,7 +4453,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4464,7 +4461,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4472,7 +4469,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -4480,7 +4477,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -4488,7 +4485,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -4550,7 +4547,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4574,7 +4571,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4582,7 +4579,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4590,7 +4587,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -4598,7 +4595,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -4606,7 +4603,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -4614,7 +4611,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -4622,7 +4619,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -4630,7 +4627,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -4683,7 +4680,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4691,7 +4688,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4699,7 +4696,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4707,7 +4704,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4715,7 +4712,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4723,7 +4720,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4731,7 +4728,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4739,7 +4736,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4777,7 +4774,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4785,7 +4782,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4793,7 +4790,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4801,7 +4798,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4809,7 +4806,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4817,7 +4814,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4825,7 +4822,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4833,7 +4830,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4841,7 +4838,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -4849,7 +4846,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -4857,7 +4854,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -4865,7 +4862,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -4873,7 +4870,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -4906,7 +4903,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4914,7 +4911,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4922,7 +4919,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4930,7 +4927,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4938,7 +4935,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4946,7 +4943,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4954,7 +4951,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4984,7 +4981,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5000,7 +4997,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -5032,7 +5029,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5048,7 +5045,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -5064,7 +5061,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5072,7 +5069,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -5080,7 +5077,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -5088,7 +5085,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -5096,7 +5093,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -5104,7 +5101,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -5137,7 +5134,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5161,7 +5158,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5169,7 +5166,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5177,7 +5174,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -5185,7 +5182,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5193,7 +5190,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5201,7 +5198,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -5209,7 +5206,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -5217,7 +5214,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5271,7 +5268,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5303,7 +5300,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5327,7 +5324,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5335,7 +5332,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -5343,7 +5340,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -5351,7 +5348,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -5359,7 +5356,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -5367,7 +5364,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -5375,7 +5372,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>38</v>
@@ -5383,7 +5380,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>39</v>
@@ -5413,7 +5410,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5421,7 +5418,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -5429,7 +5426,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -5437,7 +5434,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5445,7 +5442,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5453,7 +5450,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -5461,7 +5458,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5469,7 +5466,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5499,7 +5496,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5507,7 +5504,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -5515,7 +5512,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -5523,7 +5520,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5531,7 +5528,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5539,7 +5536,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -5547,7 +5544,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5555,7 +5552,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5563,7 +5560,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -5571,7 +5568,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -5579,7 +5576,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5612,7 +5609,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5620,7 +5617,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -5636,7 +5633,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5644,7 +5641,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5652,7 +5649,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -5660,7 +5657,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5668,7 +5665,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5676,7 +5673,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -5684,7 +5681,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -5692,7 +5689,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5700,7 +5697,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="777" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60A07118-26AE-424F-94B9-87B92881907B}"/>
+  <xr:revisionPtr revIDLastSave="778" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{845FC894-5185-42AC-91E4-2197FCE85EC6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="361">
   <si>
     <t>Team</t>
   </si>
@@ -235,9 +235,6 @@
   </si>
   <si>
     <t>Merrimack</t>
-  </si>
-  <si>
-    <t>Long Island</t>
   </si>
   <si>
     <t>UMBC</t>
@@ -1609,7 +1606,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -1642,7 +1639,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -1653,7 +1650,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -1675,7 +1672,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -1719,7 +1716,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -1730,7 +1727,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
@@ -1752,7 +1749,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
@@ -1763,7 +1760,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -1774,7 +1771,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
@@ -1785,7 +1782,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -1807,7 +1804,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -1818,7 +1815,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -1840,7 +1837,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1851,7 +1848,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -1862,7 +1859,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
@@ -1884,7 +1881,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
@@ -1895,7 +1892,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -1906,7 +1903,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
@@ -1917,7 +1914,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
@@ -1928,7 +1925,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
@@ -1939,10 +1936,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>5</v>
@@ -1953,7 +1950,7 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>6</v>
@@ -1964,7 +1961,7 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>7</v>
@@ -1972,10 +1969,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>8</v>
@@ -1983,10 +1980,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>9</v>
@@ -1994,10 +1991,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>10</v>
@@ -2005,10 +2002,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>11</v>
@@ -2016,10 +2013,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>12</v>
@@ -2027,10 +2024,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>13</v>
@@ -2041,7 +2038,7 @@
         <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>14</v>
@@ -2049,10 +2046,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>15</v>
@@ -2060,10 +2057,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>16</v>
@@ -2074,7 +2071,7 @@
         <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>17</v>
@@ -2082,10 +2079,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>18</v>
@@ -2096,7 +2093,7 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>19</v>
@@ -2104,10 +2101,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>41</v>
@@ -2115,10 +2112,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>42</v>
@@ -2126,10 +2123,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>5</v>
@@ -2137,10 +2134,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>6</v>
@@ -2148,10 +2145,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>7</v>
@@ -2162,7 +2159,7 @@
         <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>8</v>
@@ -2173,7 +2170,7 @@
         <v>23</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>9</v>
@@ -2184,7 +2181,7 @@
         <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>10</v>
@@ -2195,7 +2192,7 @@
         <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>11</v>
@@ -2206,7 +2203,7 @@
         <v>50</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>12</v>
@@ -2217,7 +2214,7 @@
         <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>13</v>
@@ -2225,10 +2222,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>14</v>
@@ -2236,10 +2233,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>15</v>
@@ -2247,10 +2244,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>16</v>
@@ -2258,10 +2255,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>17</v>
@@ -2272,7 +2269,7 @@
         <v>54</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>18</v>
@@ -2280,10 +2277,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>19</v>
@@ -2291,10 +2288,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>56</v>
+        <v>307</v>
       </c>
       <c r="B69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>20</v>
@@ -2350,7 +2347,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2366,7 +2363,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2398,7 +2395,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2406,7 +2403,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2414,7 +2411,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -2422,7 +2419,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -2430,7 +2427,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -2438,7 +2435,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -2446,7 +2443,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -2454,7 +2451,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -2462,7 +2459,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -2500,7 +2497,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2516,7 +2513,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2524,7 +2521,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2532,7 +2529,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2540,7 +2537,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2548,7 +2545,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2556,7 +2553,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2564,7 +2561,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -2572,7 +2569,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -2580,7 +2577,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -2618,7 +2615,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2626,7 +2623,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2634,7 +2631,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2642,7 +2639,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2650,7 +2647,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2658,7 +2655,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2666,7 +2663,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2674,7 +2671,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2682,7 +2679,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -2712,7 +2709,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -2720,7 +2717,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2728,7 +2725,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2736,7 +2733,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2744,7 +2741,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2752,7 +2749,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2760,7 +2757,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2768,7 +2765,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2776,7 +2773,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2814,7 +2811,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2822,7 +2819,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2830,7 +2827,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2838,7 +2835,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2846,7 +2843,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2854,7 +2851,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2862,7 +2859,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2870,7 +2867,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -2878,7 +2875,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -2886,7 +2883,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -2894,7 +2891,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -2902,7 +2899,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -2932,7 +2929,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -2940,7 +2937,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -2948,7 +2945,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -2956,7 +2953,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -2964,7 +2961,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -2972,7 +2969,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -2980,7 +2977,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -2988,7 +2985,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -2996,7 +2993,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3004,7 +3001,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3034,7 +3031,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3042,7 +3039,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3050,7 +3047,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3058,7 +3055,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3066,7 +3063,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3074,7 +3071,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3082,7 +3079,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3090,7 +3087,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3098,7 +3095,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3106,7 +3103,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3136,7 +3133,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3144,7 +3141,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3152,7 +3149,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3160,7 +3157,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3168,7 +3165,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3176,7 +3173,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3184,7 +3181,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3192,7 +3189,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3200,7 +3197,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3208,7 +3205,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3246,7 +3243,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3254,7 +3251,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3262,7 +3259,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3270,7 +3267,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3278,7 +3275,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3286,7 +3283,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3294,7 +3291,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3333,7 +3330,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3341,7 +3338,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3349,7 +3346,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3357,7 +3354,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3365,7 +3362,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3373,7 +3370,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3381,7 +3378,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3389,7 +3386,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3427,7 +3424,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3435,7 +3432,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3443,7 +3440,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3451,7 +3448,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3459,7 +3456,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3467,7 +3464,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3475,7 +3472,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3483,7 +3480,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3491,7 +3488,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3499,7 +3496,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -3507,7 +3504,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -3515,7 +3512,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -3523,7 +3520,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -3562,7 +3559,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3570,7 +3567,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3578,7 +3575,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3586,7 +3583,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3594,7 +3591,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3602,7 +3599,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3610,7 +3607,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3618,7 +3615,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3626,7 +3623,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3634,7 +3631,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3642,7 +3639,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -3650,7 +3647,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -3680,7 +3677,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3688,7 +3685,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3696,7 +3693,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3704,7 +3701,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3712,7 +3709,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3720,7 +3717,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3728,7 +3725,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3736,7 +3733,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3744,7 +3741,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3752,7 +3749,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3791,7 +3788,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3799,7 +3796,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3807,7 +3804,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3815,7 +3812,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3823,7 +3820,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3831,7 +3828,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3839,7 +3836,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3847,7 +3844,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3885,7 +3882,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -3893,7 +3890,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -3901,7 +3898,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -3909,7 +3906,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3917,7 +3914,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -3925,7 +3922,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -3933,7 +3930,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -3941,7 +3938,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -3949,7 +3946,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -3957,7 +3954,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -3992,7 +3989,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4000,7 +3997,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4008,7 +4005,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4046,7 +4043,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4054,7 +4051,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4062,7 +4059,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4070,7 +4067,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4078,7 +4075,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4086,7 +4083,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4094,7 +4091,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4102,7 +4099,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4110,7 +4107,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -4141,7 +4138,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4149,7 +4146,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4157,7 +4154,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4165,7 +4162,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4173,7 +4170,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4181,7 +4178,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4189,7 +4186,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4219,7 +4216,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4227,7 +4224,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4235,7 +4232,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4243,7 +4240,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4251,7 +4248,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4259,7 +4256,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4267,7 +4264,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4275,7 +4272,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4305,7 +4302,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4313,7 +4310,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4321,7 +4318,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4329,7 +4326,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4337,7 +4334,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4345,7 +4342,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4353,7 +4350,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4361,7 +4358,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4397,7 +4394,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4405,7 +4402,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4413,7 +4410,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4421,7 +4418,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4429,7 +4426,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4437,7 +4434,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4445,7 +4442,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4453,7 +4450,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4461,7 +4458,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4469,7 +4466,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -4477,7 +4474,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -4485,7 +4482,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -4523,7 +4520,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4539,7 +4536,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4547,7 +4544,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4563,7 +4560,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4571,7 +4568,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4579,7 +4576,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4587,7 +4584,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -4595,7 +4592,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -4603,7 +4600,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -4611,7 +4608,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -4619,7 +4616,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -4627,7 +4624,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -4680,7 +4677,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4688,7 +4685,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4696,7 +4693,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4704,7 +4701,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4712,7 +4709,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4720,7 +4717,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4728,7 +4725,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4736,7 +4733,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4774,7 +4771,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4782,7 +4779,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4790,7 +4787,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4798,7 +4795,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4806,7 +4803,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4814,7 +4811,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4822,7 +4819,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -4830,7 +4827,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -4838,7 +4835,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -4846,7 +4843,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -4854,7 +4851,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -4862,7 +4859,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -4870,7 +4867,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -4903,7 +4900,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4911,7 +4908,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4919,7 +4916,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -4927,7 +4924,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -4935,7 +4932,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -4943,7 +4940,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -4951,7 +4948,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -4981,7 +4978,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -4989,7 +4986,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -4997,7 +4994,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -5029,7 +5026,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5037,7 +5034,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5045,7 +5042,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -5061,7 +5058,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5069,7 +5066,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -5077,7 +5074,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -5085,7 +5082,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -5093,7 +5090,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -5101,7 +5098,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -5134,7 +5131,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5158,7 +5155,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5166,7 +5163,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5174,7 +5171,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -5182,7 +5179,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5190,7 +5187,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5198,7 +5195,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -5206,7 +5203,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -5214,7 +5211,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5244,7 +5241,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5252,7 +5249,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -5268,7 +5265,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5276,7 +5273,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5300,7 +5297,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5316,7 +5313,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -5324,7 +5321,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5332,7 +5329,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -5340,7 +5337,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -5348,7 +5345,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
@@ -5356,7 +5353,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>19</v>
@@ -5364,7 +5361,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -5372,7 +5369,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>38</v>
@@ -5380,7 +5377,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>39</v>
@@ -5410,7 +5407,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5418,7 +5415,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -5426,7 +5423,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -5434,7 +5431,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5442,7 +5439,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5450,7 +5447,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -5458,7 +5455,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5466,7 +5463,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5496,7 +5493,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5504,7 +5501,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -5512,7 +5509,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -5520,7 +5517,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5528,7 +5525,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5536,7 +5533,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -5544,7 +5541,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5552,7 +5549,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5560,7 +5557,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -5568,7 +5565,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -5576,7 +5573,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5609,7 +5606,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5617,7 +5614,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -5625,7 +5622,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -5633,7 +5630,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -5641,7 +5638,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -5649,7 +5646,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -5657,7 +5654,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -5665,7 +5662,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -5673,7 +5670,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
@@ -5681,7 +5678,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -5689,7 +5686,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
@@ -5697,7 +5694,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="778" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{845FC894-5185-42AC-91E4-2197FCE85EC6}"/>
+  <xr:revisionPtr revIDLastSave="839" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A54586AA-7FB9-43D7-9430-77EEB7F5C445}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
@@ -1573,7 +1573,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
@@ -1672,7 +1672,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>199</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -1716,7 +1716,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -1727,150 +1727,150 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>258</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>169</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>226</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>219</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
         <v>57</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
         <v>57</v>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
         <v>57</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
         <v>57</v>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
         <v>57</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="B44" t="s">
         <v>57</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="B45" t="s">
         <v>57</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
         <v>57</v>
@@ -2046,79 +2046,79 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="B49" t="s">
         <v>57</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>199</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s">
         <v>57</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="B52" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="B53" t="s">
         <v>57</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -2145,7 +2145,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
         <v>74</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B57" t="s">
         <v>74</v>
@@ -2167,7 +2167,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B58" t="s">
         <v>74</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="B60" t="s">
         <v>74</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="B63" t="s">
         <v>74</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
         <v>74</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>146</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
         <v>74</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>355</v>
+        <v>53</v>
       </c>
       <c r="B66" t="s">
         <v>74</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B67" t="s">
         <v>74</v>
@@ -2288,7 +2288,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B69" t="s">
         <v>74</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="839" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A54586AA-7FB9-43D7-9430-77EEB7F5C445}"/>
+  <xr:revisionPtr revIDLastSave="840" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB64680-FED4-4AC9-BE55-8824CB0CA368}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="840" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB64680-FED4-4AC9-BE55-8824CB0CA368}"/>
+  <xr:revisionPtr revIDLastSave="882" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{789EF371-3479-479E-B010-A66748873DB9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -1661,464 +1661,464 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>199</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>247</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>293</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>259</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>226</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>322</v>
+        <v>219</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>219</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>57</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
         <v>57</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
         <v>57</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
         <v>57</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
         <v>57</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
         <v>57</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
         <v>57</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
         <v>57</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
         <v>57</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B46" t="s">
         <v>57</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>146</v>
+        <v>355</v>
       </c>
       <c r="B49" t="s">
         <v>57</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>355</v>
+        <v>35</v>
       </c>
       <c r="B50" t="s">
         <v>57</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>307</v>
+        <v>262</v>
       </c>
       <c r="B53" t="s">
         <v>57</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -2178,7 +2178,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B59" t="s">
         <v>74</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B64" t="s">
         <v>74</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>53</v>
+        <v>231</v>
       </c>
       <c r="B66" t="s">
         <v>74</v>
@@ -2288,7 +2288,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B69" t="s">
         <v>74</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="882" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{789EF371-3479-479E-B010-A66748873DB9}"/>
+  <xr:revisionPtr revIDLastSave="938" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D472E096-68E2-4DD7-8654-200ACE6CBEF2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -1573,7 +1573,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -1661,156 +1661,156 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>293</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>293</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -1821,45 +1821,45 @@
         <v>37</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>231</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>199</v>
+        <v>355</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
         <v>57</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
         <v>57</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
         <v>57</v>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
         <v>57</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
         <v>57</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
         <v>57</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
         <v>57</v>
@@ -2035,200 +2035,200 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
         <v>57</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>355</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
         <v>57</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B50" t="s">
         <v>57</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>262</v>
       </c>
       <c r="B52" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="B54" t="s">
         <v>74</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
         <v>74</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
         <v>74</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B57" t="s">
         <v>74</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B58" t="s">
         <v>74</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B59" t="s">
         <v>74</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="B60" t="s">
         <v>74</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B61" t="s">
         <v>74</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B62" t="s">
         <v>74</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="B63" t="s">
         <v>74</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -2239,12 +2239,12 @@
         <v>74</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="B65" t="s">
         <v>74</v>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="B66" t="s">
         <v>74</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>247</v>
       </c>
       <c r="B68" t="s">
         <v>74</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="938" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D472E096-68E2-4DD7-8654-200ACE6CBEF2}"/>
+  <xr:revisionPtr revIDLastSave="982" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{150ACA6E-9C6F-4E5E-ACCD-83949B760A67}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>146</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -1716,7 +1716,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>231</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>226</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
         <v>57</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
         <v>57</v>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
         <v>57</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="B42" t="s">
         <v>57</v>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
         <v>57</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="B44" t="s">
         <v>57</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
         <v>57</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
         <v>57</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>210</v>
+        <v>146</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s">
         <v>57</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>247</v>
       </c>
       <c r="B50" t="s">
         <v>57</v>
@@ -2090,7 +2090,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>219</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
         <v>74</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B57" t="s">
         <v>74</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B59" t="s">
         <v>74</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
         <v>74</v>
@@ -2200,7 +2200,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B61" t="s">
         <v>74</v>
@@ -2211,7 +2211,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="s">
         <v>74</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>231</v>
       </c>
       <c r="B65" t="s">
         <v>74</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="B68" t="s">
         <v>74</v>
@@ -2288,7 +2288,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>307</v>
+        <v>73</v>
       </c>
       <c r="B69" t="s">
         <v>74</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="982" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{150ACA6E-9C6F-4E5E-ACCD-83949B760A67}"/>
+  <xr:revisionPtr revIDLastSave="1008" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861B2C12-16D7-4C43-824E-CB99AA3ACCB6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="363">
   <si>
     <t>Team</t>
   </si>
@@ -1150,6 +1150,12 @@
   </si>
   <si>
     <t>Tarleton St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akron </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIU Brooklyn </t>
   </si>
 </sst>
 </file>
@@ -1595,7 +1601,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1628,7 +1634,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -1672,7 +1678,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -1683,7 +1689,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>361</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
@@ -1694,7 +1700,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -1727,7 +1733,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>362</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
@@ -1771,7 +1777,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
@@ -1804,7 +1810,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -1815,7 +1821,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -1848,7 +1854,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -1870,7 +1876,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>355</v>
+        <v>199</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -1892,7 +1898,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>307</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -1903,7 +1909,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>324</v>
+        <v>213</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
@@ -1914,7 +1920,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>214</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
@@ -1991,7 +1997,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
         <v>57</v>
@@ -2002,7 +2008,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
         <v>57</v>
@@ -2046,7 +2052,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
@@ -2057,7 +2063,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
@@ -2068,7 +2074,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>89</v>
+        <v>266</v>
       </c>
       <c r="B49" t="s">
         <v>57</v>
@@ -2134,7 +2140,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B55" t="s">
         <v>74</v>
@@ -2156,7 +2162,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B57" t="s">
         <v>74</v>
@@ -2244,7 +2250,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>231</v>
+        <v>86</v>
       </c>
       <c r="B65" t="s">
         <v>74</v>
@@ -2255,7 +2261,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>199</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
         <v>74</v>
@@ -2266,7 +2272,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B67" t="s">
         <v>74</v>

--- a/ProjectedBrackets.xlsx
+++ b/ProjectedBrackets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9f237e831f26750/Jupyter/Business/MM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1008" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861B2C12-16D7-4C43-824E-CB99AA3ACCB6}"/>
+  <xr:revisionPtr revIDLastSave="1064" documentId="8_{DC458501-F46D-487D-A95A-F0D26D9143CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA88CB11-2F4F-4DB0-9283-5AE84EF90F40}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6E9E6780-D9B8-4788-9082-4844BD7B8591}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="361">
   <si>
     <t>Team</t>
   </si>
@@ -1150,12 +1150,6 @@
   </si>
   <si>
     <t>Tarleton St</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akron </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIU Brooklyn </t>
   </si>
 </sst>
 </file>
@@ -1568,7 +1562,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -1579,7 +1573,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -1590,7 +1584,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -1623,7 +1617,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -1656,7 +1650,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -1667,392 +1661,392 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>361</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>146</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>226</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>293</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>362</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>199</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>329</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="B37" t="s">
         <v>57</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
         <v>57</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
         <v>57</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
         <v>57</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
         <v>57</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
         <v>57</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="B43" t="s">
         <v>57</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
         <v>57</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
         <v>57</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B46" t="s">
         <v>57</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
@@ -2063,7 +2057,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
@@ -2074,7 +2068,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>266</v>
+        <v>36</v>
       </c>
       <c r="B49" t="s">
         <v>57</v>
@@ -2085,7 +2079,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>247</v>
+        <v>89</v>
       </c>
       <c r="B50" t="s">
         <v>57</v>
@@ -2096,7 +2090,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>219</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
@@ -2107,7 +2101,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>262</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
         <v>57</v>
@@ -2129,7 +2123,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B54" t="s">
         <v>74</v>
@@ -2140,7 +2134,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
         <v>74</v>
@@ -2151,7 +2145,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="B56" t="s">
         <v>74</v>
@@ -2195,7 +2189,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="B60" t="s">
         <v>74</v>
@@ -2206,7 +2200,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="B61" t="s">
         <v>74</v>
@@ -2217,7 +2211,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B62" t="s">
         <v>74</v>
@@ -2228,7 +2222,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B63" t="s">
         <v>74</v>
@@ -2261,7 +2255,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>35</v>
+        <v>266</v>
       </c>
       <c r="B66" t="s">
         <v>74</v>
@@ -2272,7 +2266,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="B67" t="s">
         <v>74</v>
@@ -2283,7 +2277,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="B68" t="s">
         <v>74</v>
@@ -2294,7 +2288,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>307</v>
       </c>
       <c r="B69" t="s">
         <v>74</v>
